--- a/results/job_matches_2026-09-09.xlsx
+++ b/results/job_matches_2026-09-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Infrastructure Engineer – AWS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8113d275f4e8b6</t>
+          <t>https://www.indeed.com/viewjob?jk=78929cf2e606fde4</t>
         </is>
       </c>
     </row>
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d46de95576211b34</t>
+          <t>https://www.indeed.com/viewjob?jk=6c8113d275f4e8b6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer, Cloud Infrastructure (Multiple Seniority Levels)</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Carlos, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, ECS, IAM, RDS</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87f3f2554ec8def</t>
+          <t>https://www.indeed.com/viewjob?jk=d46de95576211b34</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer II, Data (Cloud &amp; AI)</t>
+          <t>Software Engineer, Cloud Infrastructure (Multiple Seniority Levels)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>San Carlos, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, IAM, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c022ecfcaf20c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f87f3f2554ec8def</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Azure Architect</t>
+          <t>Engineer II, Data (Cloud &amp; AI)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FSS Government Solutions</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Blob Storage, Scala</t>
+          <t>AWS, Glue, Lambda, Athena, S3, IAM, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c906b9319ac1927</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c022ecfcaf20c6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TP-LINK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, Hadoop, Hive, Sqoop, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb3c79369e1483f</t>
+          <t>https://www.indeed.com/viewjob?jk=39ca6ce91460b142</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40929f510d8aea9b</t>
+          <t>https://www.indeed.com/viewjob?jk=deb3c79369e1483f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LOJELIS US</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389f31eefdd51556</t>
+          <t>https://www.indeed.com/viewjob?jk=40929f510d8aea9b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>LOJELIS US</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eea810b05366ae21</t>
+          <t>https://www.indeed.com/viewjob?jk=389f31eefdd51556</t>
         </is>
       </c>
     </row>
@@ -853,25 +853,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Paramount Global US Inc</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Advance, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2c79d681f361c1</t>
+          <t>https://www.indeed.com/viewjob?jk=eea810b05366ae21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Paramount Global US Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Advance, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2851eefe207f3714</t>
+          <t>https://www.indeed.com/viewjob?jk=5c2c79d681f361c1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8708b9448e952fad</t>
+          <t>https://www.indeed.com/viewjob?jk=2851eefe207f3714</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Infrastructure Solutions Architect</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ThinkMirum, Inc.</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Henrico, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7540868c3f94cca8</t>
+          <t>https://www.indeed.com/viewjob?jk=669507442371cba5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Terrabis</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Dimension Tables, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ab0aae8b810da1</t>
+          <t>https://www.indeed.com/viewjob?jk=92fecc97a72ee4bd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Operations Data Engineer (On Site Only)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Zoll Medical Corporation</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606ded7f86fcb046</t>
+          <t>https://www.indeed.com/viewjob?jk=8708b9448e952fad</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Engineer — AI Platform Engineering</t>
+          <t>Operations Data Engineer (On Site Only)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Zoll Medical Corporation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, GCP, BigQuery, Scala, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11261eef85e22149</t>
+          <t>https://www.indeed.com/viewjob?jk=606ded7f86fcb046</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer — AI Platform Engineering</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Athena, IAM, RDS, GCP, BigQuery, Scala, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33ee0863e9fcfb3</t>
+          <t>https://www.indeed.com/viewjob?jk=11261eef85e22149</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer II, Analytics &amp; Modeling</t>
+          <t>Senior Software Engineer - LoopNet</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, Tableau, Jenkins</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf7c4f2948adca69</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e215170f77dd53</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>OXIO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Kafka, Cassandra, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df838957caceea8b</t>
+          <t>https://www.indeed.com/viewjob?jk=b33ee0863e9fcfb3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer (Hybrid - Indianapolis or Chicago)</t>
+          <t>Data Engineer II, Analytics &amp; Modeling</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Resultant</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, Tableau, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0690835de0e1aab</t>
+          <t>https://www.indeed.com/viewjob?jk=bf7c4f2948adca69</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer (Hybrid - Indianapolis or Dallas)</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Resultant</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa37629ae83aa444</t>
+          <t>https://www.indeed.com/viewjob?jk=b6aa2dd2deec446d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Engineer III - Platform Data Engineer (Remote)</t>
+          <t>Backend Software Engineer, Agentic Data Platform-NYC (Tapestry)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>X Development</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4b81b7d3a7707c</t>
+          <t>https://www.indeed.com/viewjob?jk=770fe58ee0737008</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>OXIO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, IAM, RDS, Azure, Kafka, Cassandra, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7318de585b9240c9</t>
+          <t>https://www.indeed.com/viewjob?jk=df838957caceea8b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior DevOps Cloud Engineer (Hybrid - Indianapolis or Chicago)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Resultant</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a63e8d41e47b1d</t>
+          <t>https://www.indeed.com/viewjob?jk=e0690835de0e1aab</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior DevOps Cloud Engineer (Hybrid - Indianapolis or Dallas)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Resultant</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfdc237a5ec2521a</t>
+          <t>https://www.indeed.com/viewjob?jk=aa37629ae83aa444</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Engineer III - Platform Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Long Key, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=860b23040114a8d8</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4b81b7d3a7707c</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96dbbd28de91d8d7</t>
+          <t>https://www.indeed.com/viewjob?jk=7318de585b9240c9</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f7a086e893f74d3</t>
+          <t>https://www.indeed.com/viewjob?jk=39a63e8d41e47b1d</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b76ff97226a6fc</t>
+          <t>https://www.indeed.com/viewjob?jk=bfdc237a5ec2521a</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Middletown, DE, US USA</t>
+          <t>Long Key, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c823f162806160da</t>
+          <t>https://www.indeed.com/viewjob?jk=860b23040114a8d8</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42745e2b7d3b4f70</t>
+          <t>https://www.indeed.com/viewjob?jk=96dbbd28de91d8d7</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86dbb6e245ef6f03</t>
+          <t>https://www.indeed.com/viewjob?jk=0f7a086e893f74d3</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803cad2315014c66</t>
+          <t>https://www.indeed.com/viewjob?jk=92b76ff97226a6fc</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>Middletown, DE, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21001c0e4015b94c</t>
+          <t>https://www.indeed.com/viewjob?jk=c823f162806160da</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=067ba8dc4ea90456</t>
+          <t>https://www.indeed.com/viewjob?jk=42745e2b7d3b4f70</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hope Hull, AL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca747d14a8213963</t>
+          <t>https://www.indeed.com/viewjob?jk=86dbb6e245ef6f03</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100a2578e0de9a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=803cad2315014c66</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b27b5a5a2dbd7b8</t>
+          <t>https://www.indeed.com/viewjob?jk=21001c0e4015b94c</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7650cf6efa152d46</t>
+          <t>https://www.indeed.com/viewjob?jk=067ba8dc4ea90456</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Hope Hull, AL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fdab35fb5d301b8</t>
+          <t>https://www.indeed.com/viewjob?jk=ca747d14a8213963</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8d9249e36a5a6f6</t>
+          <t>https://www.indeed.com/viewjob?jk=100a2578e0de9a9a</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hot Springs Village, AR, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dfa47cceff7481b</t>
+          <t>https://www.indeed.com/viewjob?jk=0b27b5a5a2dbd7b8</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Corrales, NM, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32034eb11b34213</t>
+          <t>https://www.indeed.com/viewjob?jk=7650cf6efa152d46</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9451dd40e73a7e8</t>
+          <t>https://www.indeed.com/viewjob?jk=5fdab35fb5d301b8</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80a95d3d6ee6292</t>
+          <t>https://www.indeed.com/viewjob?jk=b8d9249e36a5a6f6</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Hot Springs Village, AR, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de47c019dcb8f48a</t>
+          <t>https://www.indeed.com/viewjob?jk=9dfa47cceff7481b</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, US USA</t>
+          <t>Corrales, NM, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3900a08ed626684f</t>
+          <t>https://www.indeed.com/viewjob?jk=b32034eb11b34213</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=592a07a140bc3c31</t>
+          <t>https://www.indeed.com/viewjob?jk=c9451dd40e73a7e8</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fremont, NH, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d85fc6a7df757e7</t>
+          <t>https://www.indeed.com/viewjob?jk=c80a95d3d6ee6292</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=012126d96bacab86</t>
+          <t>https://www.indeed.com/viewjob?jk=de47c019dcb8f48a</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Okemos, MI, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25faed0ee0f87e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=3900a08ed626684f</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f528d7c6591cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=592a07a140bc3c31</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Fremont, NH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd1b53baaf5bb73e</t>
+          <t>https://www.indeed.com/viewjob?jk=4d85fc6a7df757e7</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4e0147cefbb8eb1</t>
+          <t>https://www.indeed.com/viewjob?jk=012126d96bacab86</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Okemos, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be56d1f6c8fed56c</t>
+          <t>https://www.indeed.com/viewjob?jk=25faed0ee0f87e0b</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724cac9c095efeeb</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f528d7c6591cc6</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New Franken, WI, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad205890083815e</t>
+          <t>https://www.indeed.com/viewjob?jk=bd1b53baaf5bb73e</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6ee3ad0f2f5a12f</t>
+          <t>https://www.indeed.com/viewjob?jk=e4e0147cefbb8eb1</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e639c4f4fc356279</t>
+          <t>https://www.indeed.com/viewjob?jk=be56d1f6c8fed56c</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0bc7bce3b199252</t>
+          <t>https://www.indeed.com/viewjob?jk=724cac9c095efeeb</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>New Franken, WI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02ce8ad5ba0ffc3</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad205890083815e</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e42009318b0530</t>
+          <t>https://www.indeed.com/viewjob?jk=a6ee3ad0f2f5a12f</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5620acaf132d6433</t>
+          <t>https://www.indeed.com/viewjob?jk=e639c4f4fc356279</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85ded7658087672f</t>
+          <t>https://www.indeed.com/viewjob?jk=b0bc7bce3b199252</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c301099fdc12e291</t>
+          <t>https://www.indeed.com/viewjob?jk=d02ce8ad5ba0ffc3</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96c1789a53f8e267</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e42009318b0530</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Upper Darby, PA, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803b2cfe22724310</t>
+          <t>https://www.indeed.com/viewjob?jk=5620acaf132d6433</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=805ba729e77c2f20</t>
+          <t>https://www.indeed.com/viewjob?jk=85ded7658087672f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d19e49393e61c3</t>
+          <t>https://www.indeed.com/viewjob?jk=c301099fdc12e291</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=516c0cec840edf60</t>
+          <t>https://www.indeed.com/viewjob?jk=96c1789a53f8e267</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Upper Darby, PA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=014c5701f0f8c8d9</t>
+          <t>https://www.indeed.com/viewjob?jk=803b2cfe22724310</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dcb99e6f3d7d62f</t>
+          <t>https://www.indeed.com/viewjob?jk=805ba729e77c2f20</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior .Net Full-Stack Engineer</t>
+          <t>AI Architect/Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24127d299155c458</t>
+          <t>https://www.indeed.com/viewjob?jk=59d19e49393e61c3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>AI Architect/Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7ddd4398f2504b</t>
+          <t>https://www.indeed.com/viewjob?jk=516c0cec840edf60</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>AI Architect/Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Reserv</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b393b7062df51c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=014c5701f0f8c8d9</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer - Azure Data Factory &amp; Snowflake</t>
+          <t>AI Architect/Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,67 +3191,67 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23f7874bd18f37c2</t>
+          <t>https://www.indeed.com/viewjob?jk=9dcb99e6f3d7d62f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Product Engineer (Databricks)</t>
+          <t>Senior .Net Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, MLflow</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64db87397886bc2f</t>
+          <t>https://www.indeed.com/viewjob?jk=24127d299155c458</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Data Integration Engineer</t>
+          <t>Dir Data Warehouse Engineering</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Compeer Financial</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Brea, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f769482011075d</t>
+          <t>https://www.indeed.com/viewjob?jk=653989f90deb93eb</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr Data Integration Engineer</t>
+          <t>Software Engineering MTS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Compeer Financial</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Lakeville, MN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9148243603cf3be</t>
+          <t>https://www.indeed.com/viewjob?jk=2bbe5469b433e310</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr Data Integration Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Compeer Financial</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Mankato, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=469ec4ce7b9f659e</t>
+          <t>https://www.indeed.com/viewjob?jk=8a7ddd4398f2504b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AWS Database Architect</t>
+          <t>Analytics Platform Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tachyon Technologies</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, IAM, RDS, Kafka, DynamoDB</t>
+          <t>AWS, RDS, Databricks, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7089341fcf260484</t>
+          <t>https://www.indeed.com/viewjob?jk=17e2fb702c156b62</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Wiliot</t>
+          <t>Reserv</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48382c1e967bcd2e</t>
+          <t>https://www.indeed.com/viewjob?jk=b393b7062df51c5e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer - Azure Data Factory &amp; Snowflake</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Wiliot</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,77 +3426,77 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=698be948a8b607b2</t>
+          <t>https://www.indeed.com/viewjob?jk=23f7874bd18f37c2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Product Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Snowflake Schema, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=547acd1166eac18c</t>
+          <t>https://www.indeed.com/viewjob?jk=64db87397886bc2f</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ETL Tester with AI Experience</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, dbt, MLflow</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d0d3ecc1106859</t>
+          <t>https://www.indeed.com/viewjob?jk=80e719ce5a357916</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Sr Data Integration Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Landmark Properties, Inc.</t>
+          <t>Compeer Financial</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Athens, GA, US USA</t>
+          <t>Mankato, MN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e98e4f56ed833c2</t>
+          <t>https://www.indeed.com/viewjob?jk=469ec4ce7b9f659e</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Sr Data Integration Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Landmark Properties, Inc.</t>
+          <t>Compeer Financial</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eec69955d73cd72</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f769482011075d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Speech &amp; LLM Training Data</t>
+          <t>Sr Data Integration Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Propio LS LLC</t>
+          <t>Compeer Financial</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Lakeville, MN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, IAM, Databricks, Spark, PySpark, ELT, MLflow</t>
+          <t>AWS, RDS, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,94 +3611,94 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=807824f66dc0a84a</t>
+          <t>https://www.indeed.com/viewjob?jk=b9148243603cf3be</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Katalyst Data Management</t>
+          <t>Wiliot</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, PostgreSQL, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a5ab3490cf1d4af</t>
+          <t>https://www.indeed.com/viewjob?jk=48382c1e967bcd2e</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full Stack</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Wiliot</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fbaf369c2bba2b3</t>
+          <t>https://www.indeed.com/viewjob?jk=698be948a8b607b2</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Full Stack UI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Quantum US</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21984098565a1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=2f59d1ec1d618a17</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Lackland AFB, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Hive, Impala, Spark, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Snowflake Schema, ETL, dbt</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7090249009d0d6da</t>
+          <t>https://www.indeed.com/viewjob?jk=547acd1166eac18c</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Full Stack UI Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Quantum US</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Lackland AFB, TX, US USA</t>
+          <t>Centennial, CO, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Hive, Impala, Spark, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, S3, SQS, RDS, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c235a4e1abd13f7</t>
+          <t>https://www.indeed.com/viewjob?jk=f21984098565a1d3</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Azure Databricks Infrastructure Engineer</t>
+          <t>Senior Machine Learning Engineer, Speech &amp; LLM Training Data</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Propio LS LLC</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, ELT, MLflow, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Step Functions, S3, IAM, Databricks, Spark, PySpark, ELT, MLflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5e6f301d4219633</t>
+          <t>https://www.indeed.com/viewjob?jk=807824f66dc0a84a</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Landmark Properties, Inc.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Athens, GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf21b46341bfdf2</t>
+          <t>https://www.indeed.com/viewjob?jk=3e98e4f56ed833c2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr. Quality Assurance Analyst</t>
+          <t>Senior Software Engineer, Full Stack</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Broadcast Music</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d059a9776583fb9</t>
+          <t>https://www.indeed.com/viewjob?jk=0fbaf369c2bba2b3</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr. Quality Assurance Analyst</t>
+          <t>ETL Tester with AI Experience</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Broadcast Music</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, dbt, MLflow</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f947c468dcbd787</t>
+          <t>https://www.indeed.com/viewjob?jk=67d0d3ecc1106859</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Microsoft Azure Specialist</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Landmark Properties, Inc.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5427c3decfca9bb</t>
+          <t>https://www.indeed.com/viewjob?jk=8eec69955d73cd72</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lackland AFB, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Hadoop, Hive, Impala, Spark, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d18274e749f6531</t>
+          <t>https://www.indeed.com/viewjob?jk=7090249009d0d6da</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Lackland AFB, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Hadoop, Hive, Impala, Spark, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb33e1cad99b3b6</t>
+          <t>https://www.indeed.com/viewjob?jk=8c235a4e1abd13f7</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data modeler- ETL</t>
+          <t>Senior Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>KINECTIVE</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,19 +4066,19 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a609b29094569b</t>
+          <t>https://www.indeed.com/viewjob?jk=c91e3acfe1355358</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Azure Databricks Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Azure DevOps, Kubernetes, pytest, Git</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, ELT, MLflow, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d342c243987526b3</t>
+          <t>https://www.indeed.com/viewjob?jk=d5e6f301d4219633</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Python Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,19 +4136,19 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd497236bc21a443</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf21b46341bfdf2</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Developer / Engineer</t>
+          <t>Microsoft Azure Specialist</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>JOb Assist</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e4b70d4e466c6eb</t>
+          <t>https://www.indeed.com/viewjob?jk=b5427c3decfca9bb</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer II – Generative AI &amp; LLM Platforms</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, MLOps, CI/CD, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,217 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51506997cf019eed</t>
+          <t>https://www.indeed.com/viewjob?jk=4d18274e749f6531</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Enterprise Architect</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ddb33e1cad99b3b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Data modeler- ETL</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4a609b29094569b</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior Python Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>ATG</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>North Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd497236bc21a443</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer- Backend (Product &amp; Cloud Security)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Yoodli AI Roleplays</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, NoSQL, Tableau, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9874984dfeed8f80</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>FDM Group</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Azure, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Azure DevOps, Kubernetes, pytest, Git</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d342c243987526b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Software Developer / Engineer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>JOb Assist</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e4b70d4e466c6eb</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-09.xlsx
+++ b/results/job_matches_2026-09-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0037a04643c403d</t>
+          <t>https://www.indeed.com/viewjob?jk=6c8113d275f4e8b6</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8113d275f4e8b6</t>
+          <t>https://www.indeed.com/viewjob?jk=c0037a04643c403d</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>GCP Python Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb3c79369e1483f</t>
+          <t>https://www.indeed.com/viewjob?jk=b64978da5029f9c3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40929f510d8aea9b</t>
+          <t>https://www.indeed.com/viewjob?jk=8571eee74fa37144</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LOJELIS US</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389f31eefdd51556</t>
+          <t>https://www.indeed.com/viewjob?jk=5306f5b43c1fe61a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS Data Architect (Remote)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Signet Jewelers</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Akron, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, SQS, SNS, API Gateway, IAM, RDS</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3cc1b67d583e3e1</t>
+          <t>https://www.indeed.com/viewjob?jk=6250b6d758b24165</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>GCP Python Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eea810b05366ae21</t>
+          <t>https://www.indeed.com/viewjob?jk=daaa8d1691a560b0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Paramount Global US Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Advance, NC, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2c79d681f361c1</t>
+          <t>https://www.indeed.com/viewjob?jk=deb3c79369e1483f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,102 +951,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2851eefe207f3714</t>
+          <t>https://www.indeed.com/viewjob?jk=40929f510d8aea9b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>LOJELIS US</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669507442371cba5</t>
+          <t>https://www.indeed.com/viewjob?jk=389f31eefdd51556</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>AWS Data Architect (Remote)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>Signet Jewelers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Akron, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, SQS, SNS, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92fecc97a72ee4bd</t>
+          <t>https://www.indeed.com/viewjob?jk=f3cc1b67d583e3e1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8708b9448e952fad</t>
+          <t>https://www.indeed.com/viewjob?jk=eea810b05366ae21</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Operations Data Engineer (On Site Only)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Zoll Medical Corporation</t>
+          <t>Paramount Global US Inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Advance, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606ded7f86fcb046</t>
+          <t>https://www.indeed.com/viewjob?jk=5c2c79d681f361c1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Engineer — AI Platform Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, GCP, BigQuery, Scala, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, SNS, IAM, Azure, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11261eef85e22149</t>
+          <t>https://www.indeed.com/viewjob?jk=c524d2ec156b31a3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LoopNet</t>
+          <t>Data Engineer - xLT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Event Hubs, Dataflow, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3e215170f77dd53</t>
+          <t>https://www.indeed.com/viewjob?jk=24527e4fd5602bee</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33ee0863e9fcfb3</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb6a851d163dda0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer II, Analytics &amp; Modeling</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, Tableau, Jenkins</t>
+          <t>Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,102 +1231,102 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf7c4f2948adca69</t>
+          <t>https://www.indeed.com/viewjob?jk=2851eefe207f3714</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6aa2dd2deec446d</t>
+          <t>https://www.indeed.com/viewjob?jk=669507442371cba5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Backend Software Engineer, Agentic Data Platform-NYC (Tapestry)</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>X Development</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=770fe58ee0737008</t>
+          <t>https://www.indeed.com/viewjob?jk=92fecc97a72ee4bd</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>OXIO</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Kafka, Cassandra, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df838957caceea8b</t>
+          <t>https://www.indeed.com/viewjob?jk=8708b9448e952fad</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer (Hybrid - Indianapolis or Chicago)</t>
+          <t>Operations Data Engineer (On Site Only)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Resultant</t>
+          <t>Zoll Medical Corporation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0690835de0e1aab</t>
+          <t>https://www.indeed.com/viewjob?jk=606ded7f86fcb046</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer (Hybrid - Indianapolis or Dallas)</t>
+          <t>AI Engineer — AI Platform Engineering</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Resultant</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Athena, IAM, RDS, GCP, BigQuery, Scala, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa37629ae83aa444</t>
+          <t>https://www.indeed.com/viewjob?jk=11261eef85e22149</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Engineer III - Platform Data Engineer (Remote)</t>
+          <t>Senior Software Engineer - LoopNet</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4b81b7d3a7707c</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e215170f77dd53</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7318de585b9240c9</t>
+          <t>https://www.indeed.com/viewjob?jk=b33ee0863e9fcfb3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Data Engineer II, Analytics &amp; Modeling</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, Tableau, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a63e8d41e47b1d</t>
+          <t>https://www.indeed.com/viewjob?jk=bf7c4f2948adca69</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Associate, Data Operations</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Bank OZK</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfdc237a5ec2521a</t>
+          <t>https://www.indeed.com/viewjob?jk=e643dff32a837e1d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Long Key, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=860b23040114a8d8</t>
+          <t>https://www.indeed.com/viewjob?jk=14c4f20a82a492aa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96dbbd28de91d8d7</t>
+          <t>https://www.indeed.com/viewjob?jk=b6aa2dd2deec446d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Backend Software Engineer, Agentic Data Platform-NYC (Tapestry)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>X Development</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f7a086e893f74d3</t>
+          <t>https://www.indeed.com/viewjob?jk=770fe58ee0737008</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>OXIO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, IAM, RDS, Azure, Kafka, Cassandra, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b76ff97226a6fc</t>
+          <t>https://www.indeed.com/viewjob?jk=df838957caceea8b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior DevOps Cloud Engineer (Hybrid - Indianapolis or Chicago)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Resultant</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Middletown, DE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c823f162806160da</t>
+          <t>https://www.indeed.com/viewjob?jk=e0690835de0e1aab</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior DevOps Cloud Engineer (Hybrid - Indianapolis or Dallas)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Resultant</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42745e2b7d3b4f70</t>
+          <t>https://www.indeed.com/viewjob?jk=aa37629ae83aa444</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Engineer III - Platform Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86dbb6e245ef6f03</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4b81b7d3a7707c</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803cad2315014c66</t>
+          <t>https://www.indeed.com/viewjob?jk=7318de585b9240c9</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21001c0e4015b94c</t>
+          <t>https://www.indeed.com/viewjob?jk=39a63e8d41e47b1d</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=067ba8dc4ea90456</t>
+          <t>https://www.indeed.com/viewjob?jk=bfdc237a5ec2521a</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hope Hull, AL, US USA</t>
+          <t>Long Key, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca747d14a8213963</t>
+          <t>https://www.indeed.com/viewjob?jk=860b23040114a8d8</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100a2578e0de9a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=96dbbd28de91d8d7</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b27b5a5a2dbd7b8</t>
+          <t>https://www.indeed.com/viewjob?jk=0f7a086e893f74d3</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7650cf6efa152d46</t>
+          <t>https://www.indeed.com/viewjob?jk=92b76ff97226a6fc</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Middletown, DE, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fdab35fb5d301b8</t>
+          <t>https://www.indeed.com/viewjob?jk=c823f162806160da</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8d9249e36a5a6f6</t>
+          <t>https://www.indeed.com/viewjob?jk=42745e2b7d3b4f70</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hot Springs Village, AR, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dfa47cceff7481b</t>
+          <t>https://www.indeed.com/viewjob?jk=86dbb6e245ef6f03</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Corrales, NM, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32034eb11b34213</t>
+          <t>https://www.indeed.com/viewjob?jk=803cad2315014c66</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9451dd40e73a7e8</t>
+          <t>https://www.indeed.com/viewjob?jk=21001c0e4015b94c</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80a95d3d6ee6292</t>
+          <t>https://www.indeed.com/viewjob?jk=067ba8dc4ea90456</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Hope Hull, AL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de47c019dcb8f48a</t>
+          <t>https://www.indeed.com/viewjob?jk=ca747d14a8213963</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3900a08ed626684f</t>
+          <t>https://www.indeed.com/viewjob?jk=100a2578e0de9a9a</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=592a07a140bc3c31</t>
+          <t>https://www.indeed.com/viewjob?jk=0b27b5a5a2dbd7b8</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Fremont, NH, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d85fc6a7df757e7</t>
+          <t>https://www.indeed.com/viewjob?jk=7650cf6efa152d46</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=012126d96bacab86</t>
+          <t>https://www.indeed.com/viewjob?jk=5fdab35fb5d301b8</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Okemos, MI, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25faed0ee0f87e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=b8d9249e36a5a6f6</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>Hot Springs Village, AR, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f528d7c6591cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=9dfa47cceff7481b</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Corrales, NM, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd1b53baaf5bb73e</t>
+          <t>https://www.indeed.com/viewjob?jk=b32034eb11b34213</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4e0147cefbb8eb1</t>
+          <t>https://www.indeed.com/viewjob?jk=c9451dd40e73a7e8</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be56d1f6c8fed56c</t>
+          <t>https://www.indeed.com/viewjob?jk=c80a95d3d6ee6292</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724cac9c095efeeb</t>
+          <t>https://www.indeed.com/viewjob?jk=de47c019dcb8f48a</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New Franken, WI, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad205890083815e</t>
+          <t>https://www.indeed.com/viewjob?jk=3900a08ed626684f</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6ee3ad0f2f5a12f</t>
+          <t>https://www.indeed.com/viewjob?jk=592a07a140bc3c31</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Fremont, NH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e639c4f4fc356279</t>
+          <t>https://www.indeed.com/viewjob?jk=4d85fc6a7df757e7</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0bc7bce3b199252</t>
+          <t>https://www.indeed.com/viewjob?jk=012126d96bacab86</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Okemos, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02ce8ad5ba0ffc3</t>
+          <t>https://www.indeed.com/viewjob?jk=25faed0ee0f87e0b</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e42009318b0530</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f528d7c6591cc6</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5620acaf132d6433</t>
+          <t>https://www.indeed.com/viewjob?jk=bd1b53baaf5bb73e</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85ded7658087672f</t>
+          <t>https://www.indeed.com/viewjob?jk=e4e0147cefbb8eb1</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c301099fdc12e291</t>
+          <t>https://www.indeed.com/viewjob?jk=be56d1f6c8fed56c</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96c1789a53f8e267</t>
+          <t>https://www.indeed.com/viewjob?jk=724cac9c095efeeb</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Upper Darby, PA, US USA</t>
+          <t>New Franken, WI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803b2cfe22724310</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad205890083815e</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=805ba729e77c2f20</t>
+          <t>https://www.indeed.com/viewjob?jk=a6ee3ad0f2f5a12f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d19e49393e61c3</t>
+          <t>https://www.indeed.com/viewjob?jk=e639c4f4fc356279</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=516c0cec840edf60</t>
+          <t>https://www.indeed.com/viewjob?jk=b0bc7bce3b199252</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=014c5701f0f8c8d9</t>
+          <t>https://www.indeed.com/viewjob?jk=d02ce8ad5ba0ffc3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dcb99e6f3d7d62f</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e42009318b0530</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior .Net Full-Stack Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24127d299155c458</t>
+          <t>https://www.indeed.com/viewjob?jk=5620acaf132d6433</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Dir Data Warehouse Engineering</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brea, CA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653989f90deb93eb</t>
+          <t>https://www.indeed.com/viewjob?jk=85ded7658087672f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineering MTS</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bbe5469b433e310</t>
+          <t>https://www.indeed.com/viewjob?jk=c301099fdc12e291</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7ddd4398f2504b</t>
+          <t>https://www.indeed.com/viewjob?jk=96c1789a53f8e267</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Analytics Platform Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Upper Darby, PA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e2fb702c156b62</t>
+          <t>https://www.indeed.com/viewjob?jk=803b2cfe22724310</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Reserv</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b393b7062df51c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=805ba729e77c2f20</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer - Azure Data Factory &amp; Snowflake</t>
+          <t>Senior Guidewire Developer (PolicyCenter)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,67 +3436,67 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23f7874bd18f37c2</t>
+          <t>https://www.indeed.com/viewjob?jk=f3929e9d9282e947</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Product Engineer (Databricks)</t>
+          <t>Analytics Platform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, MLflow</t>
+          <t>AWS, RDS, Databricks, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64db87397886bc2f</t>
+          <t>https://www.indeed.com/viewjob?jk=17e2fb702c156b62</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>AI Architect/Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e719ce5a357916</t>
+          <t>https://www.indeed.com/viewjob?jk=59d19e49393e61c3</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr Data Integration Engineer</t>
+          <t>AI Architect/Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Compeer Financial</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Mankato, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=469ec4ce7b9f659e</t>
+          <t>https://www.indeed.com/viewjob?jk=516c0cec840edf60</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr Data Integration Engineer</t>
+          <t>AI Architect/Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Compeer Financial</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f769482011075d</t>
+          <t>https://www.indeed.com/viewjob?jk=014c5701f0f8c8d9</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr Data Integration Engineer</t>
+          <t>AI Architect/Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Compeer Financial</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Lakeville, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,102 +3611,102 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9148243603cf3be</t>
+          <t>https://www.indeed.com/viewjob?jk=9dcb99e6f3d7d62f</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineering MTS</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Wiliot</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48382c1e967bcd2e</t>
+          <t>https://www.indeed.com/viewjob?jk=2bbe5469b433e310</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Dir Data Warehouse Engineering</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Wiliot</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Brea, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=698be948a8b607b2</t>
+          <t>https://www.indeed.com/viewjob?jk=653989f90deb93eb</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Jenkins, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f59d1ec1d618a17</t>
+          <t>https://www.indeed.com/viewjob?jk=8a7ddd4398f2504b</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior .Net Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Snowflake Schema, ETL, dbt</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=547acd1166eac18c</t>
+          <t>https://www.indeed.com/viewjob?jk=24127d299155c458</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Full Stack UI Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Quantum US</t>
+          <t>Reserv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21984098565a1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=b393b7062df51c5e</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Speech &amp; LLM Training Data</t>
+          <t>Data Engineer - Azure Data Factory &amp; Snowflake</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Propio LS LLC</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, IAM, Databricks, Spark, PySpark, ELT, MLflow</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,67 +3821,67 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=807824f66dc0a84a</t>
+          <t>https://www.indeed.com/viewjob?jk=23f7874bd18f37c2</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Data Product Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Landmark Properties, Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Athens, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e98e4f56ed833c2</t>
+          <t>https://www.indeed.com/viewjob?jk=64db87397886bc2f</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full Stack</t>
+          <t>Sr Data Integration Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Compeer Financial</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Git</t>
+          <t>AWS, RDS, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fbaf369c2bba2b3</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f769482011075d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ETL Tester with AI Experience</t>
+          <t>Mule ESB Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, dbt, MLflow</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d0d3ecc1106859</t>
+          <t>https://www.indeed.com/viewjob?jk=2602c0fe6a2e7651</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Integration Platform Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Landmark Properties, Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eec69955d73cd72</t>
+          <t>https://www.indeed.com/viewjob?jk=8d8e2b60f9187848</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Lackland AFB, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Hive, Impala, Spark, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7090249009d0d6da</t>
+          <t>https://www.indeed.com/viewjob?jk=80e719ce5a357916</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr Data Integration Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Compeer Financial</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Lackland AFB, TX, US USA</t>
+          <t>Lakeville, MN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Hive, Impala, Spark, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c235a4e1abd13f7</t>
+          <t>https://www.indeed.com/viewjob?jk=b9148243603cf3be</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Cloud Network Engineer</t>
+          <t>Sr Data Integration Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>KINECTIVE</t>
+          <t>Compeer Financial</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Mankato, MN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,102 +4066,102 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c91e3acfe1355358</t>
+          <t>https://www.indeed.com/viewjob?jk=469ec4ce7b9f659e</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Azure Databricks Infrastructure Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wiliot</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, ELT, MLflow, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5e6f301d4219633</t>
+          <t>https://www.indeed.com/viewjob?jk=48382c1e967bcd2e</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Wiliot</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf21b46341bfdf2</t>
+          <t>https://www.indeed.com/viewjob?jk=698be948a8b607b2</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Microsoft Azure Specialist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5427c3decfca9bb</t>
+          <t>https://www.indeed.com/viewjob?jk=2f59d1ec1d618a17</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Snowflake Schema, ETL, dbt</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d18274e749f6531</t>
+          <t>https://www.indeed.com/viewjob?jk=547acd1166eac18c</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Machine Learning Engineer, Speech &amp; LLM Training Data</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Propio LS LLC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Step Functions, S3, IAM, Databricks, Spark, PySpark, ELT, MLflow</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb33e1cad99b3b6</t>
+          <t>https://www.indeed.com/viewjob?jk=807824f66dc0a84a</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data modeler- ETL</t>
+          <t>Windchill Technical Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a609b29094569b</t>
+          <t>https://www.indeed.com/viewjob?jk=b60463e64c21c500</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Python Engineer</t>
+          <t>Senior Software Engineer, Full Stack</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd497236bc21a443</t>
+          <t>https://www.indeed.com/viewjob?jk=0fbaf369c2bba2b3</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Backend (Product &amp; Cloud Security)</t>
+          <t>ETL Tester with AI Experience</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Yoodli AI Roleplays</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, NoSQL, Tableau, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, dbt, MLflow</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9874984dfeed8f80</t>
+          <t>https://www.indeed.com/viewjob?jk=67d0d3ecc1106859</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lackland AFB, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Azure DevOps, Kubernetes, pytest, Git</t>
+          <t>AWS, Hadoop, Hive, Impala, Spark, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d342c243987526b3</t>
+          <t>https://www.indeed.com/viewjob?jk=7090249009d0d6da</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Developer / Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>JOb Assist</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lackland AFB, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Hadoop, Hive, Impala, Spark, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,7 +4416,462 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e4b70d4e466c6eb</t>
+          <t>https://www.indeed.com/viewjob?jk=8c235a4e1abd13f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Cloud Network Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>KINECTIVE</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Golden, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c91e3acfe1355358</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Azure Databricks Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, ELT, MLflow, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5e6f301d4219633</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>IT Analyst III - Senior Test Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>State of Utah</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Jenkins</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=25024b299f02a2f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Java Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eaf21b46341bfdf2</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Solutions Architect - Digital Native Business (Healthtech)</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Git, Python</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11453f277a40e0ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Microsoft Azure Specialist</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5427c3decfca9bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Data Platform Architect</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d18274e749f6531</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Enterprise Architect</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ddb33e1cad99b3b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>PLM Technical Consultant</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6f53e322d89560b</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer- Backend (Product &amp; Cloud Security)</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Yoodli AI Roleplays</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, NoSQL, Tableau, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9874984dfeed8f80</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Python Engineer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>ATG</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>North Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd497236bc21a443</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>FDM Group</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Azure, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Azure DevOps, Kubernetes, pytest, Git</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d342c243987526b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Data modeler- ETL</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4a609b29094569b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-09.xlsx
+++ b/results/job_matches_2026-09-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Engineer — AI Platform Engineering</t>
+          <t>Senior Software Engineer - LoopNet</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, GCP, BigQuery, Scala, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11261eef85e22149</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e215170f77dd53</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LoopNet</t>
+          <t>AI Engineer — AI Platform Engineering</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, Athena, IAM, RDS, GCP, BigQuery, Scala, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3e215170f77dd53</t>
+          <t>https://www.indeed.com/viewjob?jk=11261eef85e22149</t>
         </is>
       </c>
     </row>
@@ -3408,17 +3408,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Guidewire Developer (PolicyCenter)</t>
+          <t>AI Architect/Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3929e9d9282e947</t>
+          <t>https://www.indeed.com/viewjob?jk=59d19e49393e61c3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Analytics Platform Engineer</t>
+          <t>AI Architect/Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e2fb702c156b62</t>
+          <t>https://www.indeed.com/viewjob?jk=516c0cec840edf60</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d19e49393e61c3</t>
+          <t>https://www.indeed.com/viewjob?jk=014c5701f0f8c8d9</t>
         </is>
       </c>
     </row>
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=516c0cec840edf60</t>
+          <t>https://www.indeed.com/viewjob?jk=9dcb99e6f3d7d62f</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Senior Guidewire Developer (PolicyCenter)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=014c5701f0f8c8d9</t>
+          <t>https://www.indeed.com/viewjob?jk=f3929e9d9282e947</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Software Engineering MTS</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dcb99e6f3d7d62f</t>
+          <t>https://www.indeed.com/viewjob?jk=2bbe5469b433e310</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineering MTS</t>
+          <t>Dir Data Warehouse Engineering</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Brea, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bbe5469b433e310</t>
+          <t>https://www.indeed.com/viewjob?jk=653989f90deb93eb</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Dir Data Warehouse Engineering</t>
+          <t>Senior .Net Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Brea, CA, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653989f90deb93eb</t>
+          <t>https://www.indeed.com/viewjob?jk=24127d299155c458</t>
         </is>
       </c>
     </row>
@@ -3723,17 +3723,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior .Net Full-Stack Engineer</t>
+          <t>Analytics Platform Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24127d299155c458</t>
+          <t>https://www.indeed.com/viewjob?jk=17e2fb702c156b62</t>
         </is>
       </c>
     </row>
@@ -3863,17 +3863,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr Data Integration Engineer</t>
+          <t>Mule ESB Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Compeer Financial</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f769482011075d</t>
+          <t>https://www.indeed.com/viewjob?jk=2602c0fe6a2e7651</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Mule ESB Developer</t>
+          <t>Integration Platform Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,14 +3926,14 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2602c0fe6a2e7651</t>
+          <t>https://www.indeed.com/viewjob?jk=8d8e2b60f9187848</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Integration Platform Developer</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d8e2b60f9187848</t>
+          <t>https://www.indeed.com/viewjob?jk=80e719ce5a357916</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Wiliot</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e719ce5a357916</t>
+          <t>https://www.indeed.com/viewjob?jk=48382c1e967bcd2e</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sr Data Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Compeer Financial</t>
+          <t>Wiliot</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Lakeville, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,17 +4021,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9148243603cf3be</t>
+          <t>https://www.indeed.com/viewjob?jk=698be948a8b607b2</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Mankato, MN, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=469ec4ce7b9f659e</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f769482011075d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Data Integration Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Wiliot</t>
+          <t>Compeer Financial</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Lakeville, MN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48382c1e967bcd2e</t>
+          <t>https://www.indeed.com/viewjob?jk=b9148243603cf3be</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Data Integration Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Wiliot</t>
+          <t>Compeer Financial</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Mankato, MN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,42 +4126,42 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=698be948a8b607b2</t>
+          <t>https://www.indeed.com/viewjob?jk=469ec4ce7b9f659e</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Business Analyst (SQL &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Unitedone health</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, Talend, dbt</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f59d1ec1d618a17</t>
+          <t>https://www.indeed.com/viewjob?jk=bcad9584a9c6b560</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Snowflake Schema, ETL, dbt</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=547acd1166eac18c</t>
+          <t>https://www.indeed.com/viewjob?jk=2f59d1ec1d618a17</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Speech &amp; LLM Training Data</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Propio LS LLC</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, IAM, Databricks, Spark, PySpark, ELT, MLflow</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Snowflake Schema, ETL, dbt</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=807824f66dc0a84a</t>
+          <t>https://www.indeed.com/viewjob?jk=547acd1166eac18c</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Windchill Technical Developer</t>
+          <t>Senior Solutions Architect</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capital Blue Cross</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60463e64c21c500</t>
+          <t>https://www.indeed.com/viewjob?jk=5ae2c6ad8ac24f2e</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full Stack</t>
+          <t>Windchill Technical Developer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fbaf369c2bba2b3</t>
+          <t>https://www.indeed.com/viewjob?jk=b60463e64c21c500</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ETL Tester with AI Experience</t>
+          <t>Senior Software Engineer, Full Stack</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, dbt, MLflow</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,67 +4346,67 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d0d3ecc1106859</t>
+          <t>https://www.indeed.com/viewjob?jk=0fbaf369c2bba2b3</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Base Administrator</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Big D Companies</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Lackland AFB, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Hive, Impala, Spark, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7090249009d0d6da</t>
+          <t>https://www.indeed.com/viewjob?jk=06360615fbf9de3a</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>ETL Tester with AI Experience</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Lackland AFB, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Hive, Impala, Spark, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, dbt, MLflow</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c235a4e1abd13f7</t>
+          <t>https://www.indeed.com/viewjob?jk=67d0d3ecc1106859</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Cloud Network Engineer</t>
+          <t>Senior Machine Learning Engineer, Speech &amp; LLM Training Data</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>KINECTIVE</t>
+          <t>Propio LS LLC</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Step Functions, S3, IAM, Databricks, Spark, PySpark, ELT, MLflow</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c91e3acfe1355358</t>
+          <t>https://www.indeed.com/viewjob?jk=807824f66dc0a84a</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Azure Databricks Infrastructure Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Katalyst Data Management</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, ELT, MLflow, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, Scala, PostgreSQL, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5e6f301d4219633</t>
+          <t>https://www.indeed.com/viewjob?jk=2a5ab3490cf1d4af</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>IT Analyst III - Senior Test Automation Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>State of Utah</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Lackland AFB, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Jenkins</t>
+          <t>AWS, Hadoop, Hive, Impala, Spark, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25024b299f02a2f9</t>
+          <t>https://www.indeed.com/viewjob?jk=7090249009d0d6da</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lackland AFB, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Hadoop, Hive, Impala, Spark, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf21b46341bfdf2</t>
+          <t>https://www.indeed.com/viewjob?jk=8c235a4e1abd13f7</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Solutions Architect - Digital Native Business (Healthtech)</t>
+          <t>Senior Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>KINECTIVE</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Git, Python</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11453f277a40e0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=c91e3acfe1355358</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Microsoft Azure Specialist</t>
+          <t>Azure Databricks Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, ELT, MLflow, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5427c3decfca9bb</t>
+          <t>https://www.indeed.com/viewjob?jk=d5e6f301d4219633</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Solutions Architect - Digital Native Business (Healthtech)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Git, Python</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d18274e749f6531</t>
+          <t>https://www.indeed.com/viewjob?jk=11453f277a40e0ce</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,14 +4696,14 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb33e1cad99b3b6</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf21b46341bfdf2</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PLM Technical Consultant</t>
+          <t>Microsoft Azure Specialist</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Terraform, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f53e322d89560b</t>
+          <t>https://www.indeed.com/viewjob?jk=b5427c3decfca9bb</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Backend (Product &amp; Cloud Security)</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Yoodli AI Roleplays</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, NoSQL, Tableau, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9874984dfeed8f80</t>
+          <t>https://www.indeed.com/viewjob?jk=4d18274e749f6531</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Python Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd497236bc21a443</t>
+          <t>https://www.indeed.com/viewjob?jk=ddb33e1cad99b3b6</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>IT Analyst III - Senior Test Automation Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>State of Utah</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Azure DevOps, Kubernetes, pytest, Git</t>
+          <t>AWS, RDS, Azure, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Jenkins</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d342c243987526b3</t>
+          <t>https://www.indeed.com/viewjob?jk=25024b299f02a2f9</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Data modeler- ETL</t>
+          <t>Senior Software Engineer- Backend (Product &amp; Cloud Security)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Yoodli AI Roleplays</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,15 +4861,85 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, NoSQL, Tableau, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9874984dfeed8f80</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Senior Python Engineer</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>ATG</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>North Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd497236bc21a443</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Data modeler- ETL</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
           <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c4a609b29094569b</t>
         </is>

--- a/results/job_matches_2026-09-09.xlsx
+++ b/results/job_matches_2026-09-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer – AWS</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>29.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, ECS, IAM</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Hadoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78929cf2e606fde4</t>
+          <t>https://www.indeed.com/viewjob?jk=8732b9fed3f420f3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Infrastructure Engineer – AWS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8113d275f4e8b6</t>
+          <t>https://www.indeed.com/viewjob?jk=78929cf2e606fde4</t>
         </is>
       </c>
     </row>
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0037a04643c403d</t>
+          <t>https://www.indeed.com/viewjob?jk=6c8113d275f4e8b6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>22.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d46de95576211b34</t>
+          <t>https://www.indeed.com/viewjob?jk=c0037a04643c403d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer, Cloud Infrastructure (Multiple Seniority Levels)</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Carlos, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, ECS, IAM, RDS</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87f3f2554ec8def</t>
+          <t>https://www.indeed.com/viewjob?jk=d46de95576211b34</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer II, Data (Cloud &amp; AI)</t>
+          <t>Software Engineer, Cloud Infrastructure (Multiple Seniority Levels)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>San Carlos, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, IAM, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,77 +671,77 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c022ecfcaf20c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f87f3f2554ec8def</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Engineer II, Data (Cloud &amp; AI)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TP-LINK</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, Hadoop, Hive, Sqoop, Spark</t>
+          <t>AWS, Glue, Lambda, Athena, S3, IAM, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ca6ce91460b142</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c022ecfcaf20c6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GCP Python Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Databricks, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b64978da5029f9c3</t>
+          <t>https://www.indeed.com/viewjob?jk=76c1021a7b6a47a3</t>
         </is>
       </c>
     </row>
@@ -753,30 +753,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Databricks, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8571eee74fa37144</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb7f514c771de53</t>
         </is>
       </c>
     </row>
@@ -788,30 +788,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Databricks, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5306f5b43c1fe61a</t>
+          <t>https://www.indeed.com/viewjob?jk=5d6c2efe2d967ca1</t>
         </is>
       </c>
     </row>
@@ -823,82 +823,82 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Databricks, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6250b6d758b24165</t>
+          <t>https://www.indeed.com/viewjob?jk=d94535e52011728f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GCP Python Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Databricks, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaa8d1691a560b0</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bc8d7737feba10</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TP-LINK</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, Hadoop, Hive, Sqoop, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb3c79369e1483f</t>
+          <t>https://www.indeed.com/viewjob?jk=39ca6ce91460b142</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40929f510d8aea9b</t>
+          <t>https://www.indeed.com/viewjob?jk=8571eee74fa37144</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LOJELIS US</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389f31eefdd51556</t>
+          <t>https://www.indeed.com/viewjob?jk=5306f5b43c1fe61a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AWS Data Architect (Remote)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Signet Jewelers</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Akron, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, SQS, SNS, API Gateway, IAM, RDS</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3cc1b67d583e3e1</t>
+          <t>https://www.indeed.com/viewjob?jk=6250b6d758b24165</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>GCP Python Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eea810b05366ae21</t>
+          <t>https://www.indeed.com/viewjob?jk=daaa8d1691a560b0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Paramount Global US Inc</t>
+          <t>LOJELIS US</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Advance, NC, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2c79d681f361c1</t>
+          <t>https://www.indeed.com/viewjob?jk=389f31eefdd51556</t>
         </is>
       </c>
     </row>
@@ -1103,90 +1103,90 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, IAM, Azure, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c524d2ec156b31a3</t>
+          <t>https://www.indeed.com/viewjob?jk=8615042a0b73fe9a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer - xLT</t>
+          <t>Data Solutions Engineer - On-site, Durham, NC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Event Hubs, Dataflow, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24527e4fd5602bee</t>
+          <t>https://www.indeed.com/viewjob?jk=37f404d54522769c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb6a851d163dda0</t>
+          <t>https://www.indeed.com/viewjob?jk=eea810b05366ae21</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Paramount Global US Inc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Advance, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,102 +1231,102 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2851eefe207f3714</t>
+          <t>https://www.indeed.com/viewjob?jk=5c2c79d681f361c1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SNS, IAM, Azure, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669507442371cba5</t>
+          <t>https://www.indeed.com/viewjob?jk=c524d2ec156b31a3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>Data Engineer - xLT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Event Hubs, Dataflow, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92fecc97a72ee4bd</t>
+          <t>https://www.indeed.com/viewjob?jk=24527e4fd5602bee</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>Trellis Company</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8708b9448e952fad</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb6a851d163dda0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Operations Data Engineer (On Site Only)</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Zoll Medical Corporation</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606ded7f86fcb046</t>
+          <t>https://www.indeed.com/viewjob?jk=2851eefe207f3714</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LoopNet</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3e215170f77dd53</t>
+          <t>https://www.indeed.com/viewjob?jk=669507442371cba5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Engineer — AI Platform Engineering</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,77 +1431,77 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, GCP, BigQuery, Scala, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11261eef85e22149</t>
+          <t>https://www.indeed.com/viewjob?jk=92fecc97a72ee4bd</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Mid/Senior-level GoLang Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Inca Digital</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33ee0863e9fcfb3</t>
+          <t>https://www.indeed.com/viewjob?jk=735a6235675ac15c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer II, Analytics &amp; Modeling</t>
+          <t>AI Engineer — AI Platform Engineering</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, Tableau, Jenkins</t>
+          <t>AWS, Athena, IAM, RDS, GCP, BigQuery, Scala, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf7c4f2948adca69</t>
+          <t>https://www.indeed.com/viewjob?jk=11261eef85e22149</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Associate, Data Operations</t>
+          <t>Senior Software Engineer - LoopNet</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bank OZK</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e643dff32a837e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e215170f77dd53</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c4f20a82a492aa</t>
+          <t>https://www.indeed.com/viewjob?jk=b33ee0863e9fcfb3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Senior Software Engineer – Cloud Data Solutions</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Coral Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6aa2dd2deec446d</t>
+          <t>https://www.indeed.com/viewjob?jk=4c874c000ec76150</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Backend Software Engineer, Agentic Data Platform-NYC (Tapestry)</t>
+          <t>Associate, Data Operations</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>X Development</t>
+          <t>Bank OZK</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=770fe58ee0737008</t>
+          <t>https://www.indeed.com/viewjob?jk=e643dff32a837e1d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OXIO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Kafka, Cassandra, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df838957caceea8b</t>
+          <t>https://www.indeed.com/viewjob?jk=14c4f20a82a492aa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer (Hybrid - Indianapolis or Chicago)</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Resultant</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0690835de0e1aab</t>
+          <t>https://www.indeed.com/viewjob?jk=b6aa2dd2deec446d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer (Hybrid - Indianapolis or Dallas)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Resultant</t>
+          <t>OXIO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Kafka, Cassandra, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa37629ae83aa444</t>
+          <t>https://www.indeed.com/viewjob?jk=df838957caceea8b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Engineer III - Platform Data Engineer (Remote)</t>
+          <t>Senior DevOps Cloud Engineer (Hybrid - Indianapolis or Chicago)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Resultant</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4b81b7d3a7707c</t>
+          <t>https://www.indeed.com/viewjob?jk=e0690835de0e1aab</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior DevOps Cloud Engineer (Hybrid - Indianapolis or Dallas)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Resultant</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7318de585b9240c9</t>
+          <t>https://www.indeed.com/viewjob?jk=aa37629ae83aa444</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Dir Data Warehouse Engineering</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Brea, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a63e8d41e47b1d</t>
+          <t>https://www.indeed.com/viewjob?jk=653989f90deb93eb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Analytics Platform Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Databricks, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfdc237a5ec2521a</t>
+          <t>https://www.indeed.com/viewjob?jk=17e2fb702c156b62</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior Guidewire Developer (PolicyCenter)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Long Key, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=860b23040114a8d8</t>
+          <t>https://www.indeed.com/viewjob?jk=f3929e9d9282e947</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Financial Consultant Partner - Woodland Hills, CA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96dbbd28de91d8d7</t>
+          <t>https://www.indeed.com/viewjob?jk=04879b45139c1c83</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior .Net Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f7a086e893f74d3</t>
+          <t>https://www.indeed.com/viewjob?jk=24127d299155c458</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Reserv</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b76ff97226a6fc</t>
+          <t>https://www.indeed.com/viewjob?jk=b393b7062df51c5e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Data Engineer - Azure Data Factory &amp; Snowflake</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Middletown, DE, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c823f162806160da</t>
+          <t>https://www.indeed.com/viewjob?jk=23f7874bd18f37c2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Data Product Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42745e2b7d3b4f70</t>
+          <t>https://www.indeed.com/viewjob?jk=64db87397886bc2f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Sr Data Integration Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Compeer Financial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86dbb6e245ef6f03</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f769482011075d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Mule ESB Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803cad2315014c66</t>
+          <t>https://www.indeed.com/viewjob?jk=2602c0fe6a2e7651</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Integration Platform Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21001c0e4015b94c</t>
+          <t>https://www.indeed.com/viewjob?jk=8d8e2b60f9187848</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=067ba8dc4ea90456</t>
+          <t>https://www.indeed.com/viewjob?jk=80e719ce5a357916</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Sr Data Integration Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Compeer Financial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hope Hull, AL, US USA</t>
+          <t>Lakeville, MN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca747d14a8213963</t>
+          <t>https://www.indeed.com/viewjob?jk=b9148243603cf3be</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Sr Data Integration Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Compeer Financial</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Mankato, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,137 +2316,137 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100a2578e0de9a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=469ec4ce7b9f659e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b27b5a5a2dbd7b8</t>
+          <t>https://www.indeed.com/viewjob?jk=223035fc7a8a7be0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Wiliot</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7650cf6efa152d46</t>
+          <t>https://www.indeed.com/viewjob?jk=48382c1e967bcd2e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Wiliot</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fdab35fb5d301b8</t>
+          <t>https://www.indeed.com/viewjob?jk=698be948a8b607b2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8d9249e36a5a6f6</t>
+          <t>https://www.indeed.com/viewjob?jk=2f59d1ec1d618a17</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hot Springs Village, AR, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Snowflake Schema, ETL, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dfa47cceff7481b</t>
+          <t>https://www.indeed.com/viewjob?jk=547acd1166eac18c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior Machine Learning Engineer, Speech &amp; LLM Training Data</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Propio LS LLC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Corrales, NM, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Glue, Step Functions, S3, IAM, Databricks, Spark, PySpark, ELT, MLflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32034eb11b34213</t>
+          <t>https://www.indeed.com/viewjob?jk=807824f66dc0a84a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Landmark Properties, Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Athens, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9451dd40e73a7e8</t>
+          <t>https://www.indeed.com/viewjob?jk=3e98e4f56ed833c2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior Solutions Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Capital Blue Cross</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80a95d3d6ee6292</t>
+          <t>https://www.indeed.com/viewjob?jk=5ae2c6ad8ac24f2e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Windchill Technical Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de47c019dcb8f48a</t>
+          <t>https://www.indeed.com/viewjob?jk=b60463e64c21c500</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Data Base Administrator</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Big D Companies</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3900a08ed626684f</t>
+          <t>https://www.indeed.com/viewjob?jk=06360615fbf9de3a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>ETL Tester with AI Experience</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, dbt, MLflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=592a07a140bc3c31</t>
+          <t>https://www.indeed.com/viewjob?jk=67d0d3ecc1106859</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior Software Engineer, Full Stack</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fremont, NH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d85fc6a7df757e7</t>
+          <t>https://www.indeed.com/viewjob?jk=0fbaf369c2bba2b3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>OSS Engineer (US - Remote)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Axon Networks</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>RDS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=012126d96bacab86</t>
+          <t>https://www.indeed.com/viewjob?jk=110b991660ad2978</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Okemos, MI, US USA</t>
+          <t>Lackland AFB, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Hadoop, Hive, Impala, Spark, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25faed0ee0f87e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=7090249009d0d6da</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>Lackland AFB, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Hadoop, Hive, Impala, Spark, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f528d7c6591cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=8c235a4e1abd13f7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>KINECTIVE</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd1b53baaf5bb73e</t>
+          <t>https://www.indeed.com/viewjob?jk=c91e3acfe1355358</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Azure Databricks Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, ELT, MLflow, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4e0147cefbb8eb1</t>
+          <t>https://www.indeed.com/viewjob?jk=d5e6f301d4219633</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Solutions Architect - Digital Native Business (Healthtech)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Git, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be56d1f6c8fed56c</t>
+          <t>https://www.indeed.com/viewjob?jk=11453f277a40e0ce</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724cac9c095efeeb</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf21b46341bfdf2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Data modeler- ETL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New Franken, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad205890083815e</t>
+          <t>https://www.indeed.com/viewjob?jk=c4a609b29094569b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior Software Engineer- Backend (Product &amp; Cloud Security)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Yoodli AI Roleplays</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, NoSQL, Tableau, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6ee3ad0f2f5a12f</t>
+          <t>https://www.indeed.com/viewjob?jk=9874984dfeed8f80</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior Python Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e639c4f4fc356279</t>
+          <t>https://www.indeed.com/viewjob?jk=cd497236bc21a443</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>IT Analyst III - Senior Test Automation Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>State of Utah</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0bc7bce3b199252</t>
+          <t>https://www.indeed.com/viewjob?jk=25024b299f02a2f9</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Microsoft Azure Specialist</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,1792 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02ce8ad5ba0ffc3</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>OR, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e42009318b0530</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Baton Rouge, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5620acaf132d6433</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>TN, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=85ded7658087672f</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Walnut Creek, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c301099fdc12e291</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Columbia, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=96c1789a53f8e267</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Upper Darby, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=803b2cfe22724310</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=805ba729e77c2f20</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>AI Architect/Developer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=59d19e49393e61c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>AI Architect/Developer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=516c0cec840edf60</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>AI Architect/Developer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=014c5701f0f8c8d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>AI Architect/Developer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9dcb99e6f3d7d62f</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior Guidewire Developer (PolicyCenter)</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Mercury Insurance Company</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f3929e9d9282e947</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Software Engineering MTS</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2bbe5469b433e310</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Dir Data Warehouse Engineering</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Mercury Insurance Company</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Brea, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=653989f90deb93eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior .Net Full-Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Brentwood, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24127d299155c458</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Python Developer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7ddd4398f2504b</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Analytics Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>PepsiCo</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=17e2fb702c156b62</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Reserv</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b393b7062df51c5e</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Data Engineer - Azure Data Factory &amp; Snowflake</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Milwaukee, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23f7874bd18f37c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Data Product Engineer (Databricks)</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, MLflow</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64db87397886bc2f</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Mule ESB Developer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2602c0fe6a2e7651</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Integration Platform Developer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d8e2b60f9187848</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Python Software Architect</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80e719ce5a357916</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Wiliot</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>San Mateo, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48382c1e967bcd2e</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Wiliot</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=698be948a8b607b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Sr Data Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Compeer Financial</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Bloomington, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f769482011075d</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Sr Data Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Compeer Financial</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Lakeville, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b9148243603cf3be</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Sr Data Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Compeer Financial</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Mankato, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=469ec4ce7b9f659e</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Business Analyst (SQL &amp; Snowflake)</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Unitedone health</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, ETL, ELT, Talend, dbt</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bcad9584a9c6b560</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Epsilon</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Jenkins, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f59d1ec1d618a17</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Data Engineer I</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Travelers</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Snowflake Schema, ETL, dbt</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=547acd1166eac18c</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Senior Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Capital Blue Cross</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, CI/CD, Jenkins, Maven</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5ae2c6ad8ac24f2e</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Windchill Technical Developer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b60463e64c21c500</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Full Stack</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0fbaf369c2bba2b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Data Base Administrator</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Big D Companies</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=06360615fbf9de3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>ETL Tester with AI Experience</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>VeeRteq Solutions Inc.</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, dbt, MLflow</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=67d0d3ecc1106859</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer, Speech &amp; LLM Training Data</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Propio LS LLC</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Overland Park, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Step Functions, S3, IAM, Databricks, Spark, PySpark, ELT, MLflow</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=807824f66dc0a84a</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Katalyst Data Management</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Scala, PostgreSQL, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a5ab3490cf1d4af</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>GRVTY</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Lackland AFB, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, Hadoop, Hive, Impala, Spark, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7090249009d0d6da</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>GRVTY</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Lackland AFB, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, Hadoop, Hive, Impala, Spark, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c235a4e1abd13f7</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Senior Cloud Network Engineer</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>KINECTIVE</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Golden, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c91e3acfe1355358</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Azure Databricks Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, ELT, MLflow, GitHub Actions, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d5e6f301d4219633</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Solutions Architect - Digital Native Business (Healthtech)</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Git, Python</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=11453f277a40e0ce</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Senior Java Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf21b46341bfdf2</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Microsoft Azure Specialist</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=b5427c3decfca9bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Data Platform Architect</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4d18274e749f6531</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Enterprise Architect</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb33e1cad99b3b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>IT Analyst III - Senior Test Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>State of Utah</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Jenkins</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=25024b299f02a2f9</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer- Backend (Product &amp; Cloud Security)</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Yoodli AI Roleplays</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, NoSQL, Tableau, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9874984dfeed8f80</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Senior Python Engineer</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>ATG</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>North Little Rock, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd497236bc21a443</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Data modeler- ETL</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a609b29094569b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-09.xlsx
+++ b/results/job_matches_2026-09-09.xlsx
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Databricks, Blob Storage</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d46de95576211b34</t>
+          <t>https://www.indeed.com/viewjob?jk=6bedb030ec88c051</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer, Cloud Infrastructure (Multiple Seniority Levels)</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Carlos, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, ECS, IAM, RDS</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87f3f2554ec8def</t>
+          <t>https://www.indeed.com/viewjob?jk=d46de95576211b34</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Engineer II, Data (Cloud &amp; AI)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, IAM, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Databricks, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c022ecfcaf20c6</t>
+          <t>https://www.indeed.com/viewjob?jk=76c1021a7b6a47a3</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c1021a7b6a47a3</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb7f514c771de53</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb7f514c771de53</t>
+          <t>https://www.indeed.com/viewjob?jk=5d6c2efe2d967ca1</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d6c2efe2d967ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=d94535e52011728f</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d94535e52011728f</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bc8d7737feba10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>TP-LINK</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Databricks, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, Hadoop, Hive, Sqoop, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bc8d7737feba10</t>
+          <t>https://www.indeed.com/viewjob?jk=39ca6ce91460b142</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>GCP Python Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TP-LINK</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, Hadoop, Hive, Sqoop, Spark</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ca6ce91460b142</t>
+          <t>https://www.indeed.com/viewjob?jk=b64978da5029f9c3</t>
         </is>
       </c>
     </row>
@@ -1063,60 +1063,60 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LOJELIS US</t>
+          <t>Globus Medical</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Audubon, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389f31eefdd51556</t>
+          <t>https://www.indeed.com/viewjob?jk=c366fd1e467d725b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8615042a0b73fe9a</t>
+          <t>https://www.indeed.com/viewjob?jk=10a3b9d686f61d33</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - On-site, Durham, NC</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37f404d54522769c</t>
+          <t>https://www.indeed.com/viewjob?jk=8615042a0b73fe9a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Data Solutions Engineer - On-site, Durham, NC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,77 +1186,77 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eea810b05366ae21</t>
+          <t>https://www.indeed.com/viewjob?jk=37f404d54522769c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Automation QE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Paramount Global US Inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Advance, NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2c79d681f361c1</t>
+          <t>https://www.indeed.com/viewjob?jk=76d03aaffe8965fd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, IAM, Azure, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c524d2ec156b31a3</t>
+          <t>https://www.indeed.com/viewjob?jk=eea810b05366ae21</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer - xLT</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Event Hubs, Dataflow, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SNS, IAM, Azure, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24527e4fd5602bee</t>
+          <t>https://www.indeed.com/viewjob?jk=c524d2ec156b31a3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Data Engineer - xLT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Trellis Company</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,52 +1326,52 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Event Hubs, Dataflow, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb6a851d163dda0</t>
+          <t>https://www.indeed.com/viewjob?jk=24527e4fd5602bee</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Stier Solutions</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Franklin, IN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2851eefe207f3714</t>
+          <t>https://www.indeed.com/viewjob?jk=8936f30be432de75</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>Mid/Senior-level GoLang Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>Inca Digital</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92fecc97a72ee4bd</t>
+          <t>https://www.indeed.com/viewjob?jk=735a6235675ac15c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mid/Senior-level GoLang Data Engineer</t>
+          <t>Senior DevOps/SRE Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Inca Digital</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=735a6235675ac15c</t>
+          <t>https://www.indeed.com/viewjob?jk=188b1c3ac78beb01</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Engineer — AI Platform Engineering</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, GCP, BigQuery, Scala, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11261eef85e22149</t>
+          <t>https://www.indeed.com/viewjob?jk=92fecc97a72ee4bd</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LoopNet</t>
+          <t>AI Engineer — AI Platform Engineering</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, Athena, IAM, RDS, GCP, BigQuery, Scala, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3e215170f77dd53</t>
+          <t>https://www.indeed.com/viewjob?jk=11261eef85e22149</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - LoopNet</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33ee0863e9fcfb3</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e215170f77dd53</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Associate, Data Operations</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bank OZK</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e643dff32a837e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=14c4f20a82a492aa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c4f20a82a492aa</t>
+          <t>https://www.indeed.com/viewjob?jk=b6aa2dd2deec446d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Associate, Data Operations</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>Bank OZK</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6aa2dd2deec446d</t>
+          <t>https://www.indeed.com/viewjob?jk=e643dff32a837e1d</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer (Hybrid - Indianapolis or Chicago)</t>
+          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Resultant</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0690835de0e1aab</t>
+          <t>https://www.indeed.com/viewjob?jk=008164574e63eb0f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer (Hybrid - Indianapolis or Dallas)</t>
+          <t>NICE Actimize Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Resultant</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,24 +1816,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa37629ae83aa444</t>
+          <t>https://www.indeed.com/viewjob?jk=7951d51dfc116951</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Dir Data Warehouse Engineering</t>
+          <t>Senior Guidewire Developer (PolicyCenter)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brea, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653989f90deb93eb</t>
+          <t>https://www.indeed.com/viewjob?jk=f3929e9d9282e947</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Analytics Platform Engineer</t>
+          <t>Dir Data Warehouse Engineering</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brea, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e2fb702c156b62</t>
+          <t>https://www.indeed.com/viewjob?jk=653989f90deb93eb</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Guidewire Developer (PolicyCenter)</t>
+          <t>Summer Associate Internship (Fraud Data Governance)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3929e9d9282e947</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa247b105a8195a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Financial Consultant Partner - Woodland Hills, CA</t>
+          <t>Summer Associate Internship (Business Intelligence Analyst)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04879b45139c1c83</t>
+          <t>https://www.indeed.com/viewjob?jk=4613876632d673e6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior .Net Full-Stack Engineer</t>
+          <t>Analytics Platform Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24127d299155c458</t>
+          <t>https://www.indeed.com/viewjob?jk=17e2fb702c156b62</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Software Engineering MTS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Reserv</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b393b7062df51c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=2bbe5469b433e310</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer - Azure Data Factory &amp; Snowflake</t>
+          <t>Summer Associate Internship (Associate Data Engineer)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23f7874bd18f37c2</t>
+          <t>https://www.indeed.com/viewjob?jk=fa822ad66fbbecb6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Product Engineer (Databricks)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,17 +2096,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, MLflow</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64db87397886bc2f</t>
+          <t>https://www.indeed.com/viewjob?jk=0de49c5b0005920d</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Mule ESB Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2602c0fe6a2e7651</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b7b991704ba53d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Integration Platform Developer</t>
+          <t>Solution Engineer - Remote</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d8e2b60f9187848</t>
+          <t>https://www.indeed.com/viewjob?jk=549bd67dfaf059ff</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Cloud Back End Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e719ce5a357916</t>
+          <t>https://www.indeed.com/viewjob?jk=979c2d51bf327a22</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Data Integration Engineer</t>
+          <t>Mule ESB Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Compeer Financial</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lakeville, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9148243603cf3be</t>
+          <t>https://www.indeed.com/viewjob?jk=2602c0fe6a2e7651</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Data Integration Engineer</t>
+          <t>Integration Platform Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Compeer Financial</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Mankato, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=469ec4ce7b9f659e</t>
+          <t>https://www.indeed.com/viewjob?jk=8d8e2b60f9187848</t>
         </is>
       </c>
     </row>
@@ -2358,87 +2358,87 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Wiliot</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48382c1e967bcd2e</t>
+          <t>https://www.indeed.com/viewjob?jk=2f59d1ec1d618a17</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Wiliot</t>
+          <t>The Consortium Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Scala, Snowflake, MySQL, dbt, CI/CD, Terraform, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=698be948a8b607b2</t>
+          <t>https://www.indeed.com/viewjob?jk=04e6bb06610c32bf</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Windchill Technical Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f59d1ec1d618a17</t>
+          <t>https://www.indeed.com/viewjob?jk=b60463e64c21c500</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Solutions Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Capital Blue Cross</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Snowflake Schema, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=547acd1166eac18c</t>
+          <t>https://www.indeed.com/viewjob?jk=5ae2c6ad8ac24f2e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Speech &amp; LLM Training Data</t>
+          <t>Data Base Administrator</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Propio LS LLC</t>
+          <t>Big D Companies</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, IAM, Databricks, Spark, PySpark, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=807824f66dc0a84a</t>
+          <t>https://www.indeed.com/viewjob?jk=06360615fbf9de3a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>ETL Tester with AI Experience</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Landmark Properties, Inc.</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Athens, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, dbt, MLflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e98e4f56ed833c2</t>
+          <t>https://www.indeed.com/viewjob?jk=67d0d3ecc1106859</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect</t>
+          <t>OSS Engineer (US - Remote)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Capital Blue Cross</t>
+          <t>Axon Networks</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ae2c6ad8ac24f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=110b991660ad2978</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Windchill Technical Developer</t>
+          <t>Quality Assurance Automation Engineer (C#)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Innocito Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,147 +2621,147 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60463e64c21c500</t>
+          <t>https://www.indeed.com/viewjob?jk=1858e1faf18bf984</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Base Administrator</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Big D Companies</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Lackland AFB, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Hadoop, Hive, Impala, Spark, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06360615fbf9de3a</t>
+          <t>https://www.indeed.com/viewjob?jk=8c235a4e1abd13f7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ETL Tester with AI Experience</t>
+          <t>Summer Associate Internship (Data Engineer)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, dbt, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d0d3ecc1106859</t>
+          <t>https://www.indeed.com/viewjob?jk=ea20d1b92e7c4c0a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full Stack</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fbaf369c2bba2b3</t>
+          <t>https://www.indeed.com/viewjob?jk=2390c91100957431</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>OSS Engineer (US - Remote)</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Axon Networks</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=110b991660ad2978</t>
+          <t>https://www.indeed.com/viewjob?jk=410d6c6a010f035c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>KINECTIVE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lackland AFB, TX, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Hive, Impala, Spark, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7090249009d0d6da</t>
+          <t>https://www.indeed.com/viewjob?jk=c91e3acfe1355358</t>
         </is>
       </c>
     </row>
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c235a4e1abd13f7</t>
+          <t>https://www.indeed.com/viewjob?jk=7090249009d0d6da</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Cloud Network Engineer</t>
+          <t>Senior Software Engineer- Backend (Product &amp; Cloud Security)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>KINECTIVE</t>
+          <t>Yoodli AI Roleplays</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, NoSQL, Tableau, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c91e3acfe1355358</t>
+          <t>https://www.indeed.com/viewjob?jk=9874984dfeed8f80</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Azure Databricks Infrastructure Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, ELT, MLflow, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5e6f301d4219633</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf21b46341bfdf2</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Microsoft Azure Specialist</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf21b46341bfdf2</t>
+          <t>https://www.indeed.com/viewjob?jk=b5427c3decfca9bb</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data modeler- ETL</t>
+          <t>AI Engineer, Enterprise AI Platform</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Camping World</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, API Gateway, ECS, Azure, GCP, Snowflake, Data Modeling, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a609b29094569b</t>
+          <t>https://www.indeed.com/viewjob?jk=d593ed18a7eaef04</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Backend (Product &amp; Cloud Security)</t>
+          <t>AI Engineer, Enterprise AI Platform</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Yoodli AI Roleplays</t>
+          <t>Camping World</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lincolnshire, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, NoSQL, Tableau, Kubernetes</t>
+          <t>AWS, API Gateway, ECS, Azure, GCP, Snowflake, Data Modeling, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9874984dfeed8f80</t>
+          <t>https://www.indeed.com/viewjob?jk=ee18a654788e5998</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Python Engineer</t>
+          <t>IT Analyst III - Senior Test Automation Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>State of Utah</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd497236bc21a443</t>
+          <t>https://www.indeed.com/viewjob?jk=25024b299f02a2f9</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>IT Analyst III - Senior Test Automation Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>State of Utah</t>
+          <t>LEADER BANK</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Arlington, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, CI/CD, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25024b299f02a2f9</t>
+          <t>https://www.indeed.com/viewjob?jk=d21460f2f100edf5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Microsoft Azure Specialist</t>
+          <t>Network Support &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,17 +3146,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5427c3decfca9bb</t>
+          <t>https://www.indeed.com/viewjob?jk=721f751b91f07d44</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-09.xlsx
+++ b/results/job_matches_2026-09-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,105 +468,105 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29.2</v>
+        <v>17.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Hadoop</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Databricks, Blob Storage</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8732b9fed3f420f3</t>
+          <t>https://www.indeed.com/viewjob?jk=6bedb030ec88c051</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer – AWS</t>
+          <t>Senior Software Engineer (Data Engineering and Infrastructure)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>AURORA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, ECS, IAM</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78929cf2e606fde4</t>
+          <t>https://www.indeed.com/viewjob?jk=62e477f85009259a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer (Data Engineering and Infrastructure)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>AURORA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8113d275f4e8b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a935b5e2a0461ce9</t>
         </is>
       </c>
     </row>
@@ -578,30 +578,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Databricks, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0037a04643c403d</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bc8d7737feba10</t>
         </is>
       </c>
     </row>
@@ -613,65 +613,65 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Databricks, Blob Storage</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Databricks, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bedb030ec88c051</t>
+          <t>https://www.indeed.com/viewjob?jk=76c1021a7b6a47a3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Databricks, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d46de95576211b34</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb7f514c771de53</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c1021a7b6a47a3</t>
+          <t>https://www.indeed.com/viewjob?jk=5d6c2efe2d967ca1</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,129 +741,129 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb7f514c771de53</t>
+          <t>https://www.indeed.com/viewjob?jk=d94535e52011728f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>TP-LINK</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Databricks, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, Hadoop, Hive, Sqoop, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d6c2efe2d967ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=39ca6ce91460b142</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GCP Python Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Databricks, Kafka, Snowflake</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d94535e52011728f</t>
+          <t>https://www.indeed.com/viewjob?jk=b64978da5029f9c3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GCP Python Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Databricks, Kafka, Snowflake</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bc8d7737feba10</t>
+          <t>https://www.indeed.com/viewjob?jk=daaa8d1691a560b0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TP-LINK</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, Hadoop, Hive, Sqoop, Spark</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ca6ce91460b142</t>
+          <t>https://www.indeed.com/viewjob?jk=5306f5b43c1fe61a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GCP Python Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b64978da5029f9c3</t>
+          <t>https://www.indeed.com/viewjob?jk=8571eee74fa37144</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,84 +951,84 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8571eee74fa37144</t>
+          <t>https://www.indeed.com/viewjob?jk=6250b6d758b24165</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Globus Medical</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Audubon, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5306f5b43c1fe61a</t>
+          <t>https://www.indeed.com/viewjob?jk=c366fd1e467d725b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6250b6d758b24165</t>
+          <t>https://www.indeed.com/viewjob?jk=10a3b9d686f61d33</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GCP Python Data Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1038,50 +1038,50 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaa8d1691a560b0</t>
+          <t>https://www.indeed.com/viewjob?jk=d75989850372d9f3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Globus Medical</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Audubon, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c366fd1e467d725b</t>
+          <t>https://www.indeed.com/viewjob?jk=b78ae98ab2be932f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10a3b9d686f61d33</t>
+          <t>https://www.indeed.com/viewjob?jk=26ce66265b66e6e9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8615042a0b73fe9a</t>
+          <t>https://www.indeed.com/viewjob?jk=d8191dfab6e9beaa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - On-site, Durham, NC</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37f404d54522769c</t>
+          <t>https://www.indeed.com/viewjob?jk=0152f97e4d45e6e2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Automation QE</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d03aaffe8965fd</t>
+          <t>https://www.indeed.com/viewjob?jk=3a6579da7d14e000</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,87 +1256,87 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eea810b05366ae21</t>
+          <t>https://www.indeed.com/viewjob?jk=8615042a0b73fe9a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions Engineer - On-site, Durham, NC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, IAM, Azure, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c524d2ec156b31a3</t>
+          <t>https://www.indeed.com/viewjob?jk=37f404d54522769c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer - xLT</t>
+          <t>Data Automation QE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Event Hubs, Dataflow, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24527e4fd5602bee</t>
+          <t>https://www.indeed.com/viewjob?jk=76d03aaffe8965fd</t>
         </is>
       </c>
     </row>
@@ -1348,82 +1348,82 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Stier Solutions</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Franklin, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Lambda, S3, SNS, IAM, Azure, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8936f30be432de75</t>
+          <t>https://www.indeed.com/viewjob?jk=c524d2ec156b31a3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>Data Engineer - xLT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Event Hubs, Dataflow, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669507442371cba5</t>
+          <t>https://www.indeed.com/viewjob?jk=24527e4fd5602bee</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mid/Senior-level GoLang Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Inca Digital</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Washington, PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=735a6235675ac15c</t>
+          <t>https://www.indeed.com/viewjob?jk=7e821a7c8c592b96</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior DevOps/SRE Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Stier Solutions</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Franklin, IN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=188b1c3ac78beb01</t>
+          <t>https://www.indeed.com/viewjob?jk=8936f30be432de75</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Engineer — AI Platform Engineering</t>
+          <t>Mid/Senior-level GoLang Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Inca Digital</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, GCP, BigQuery, Scala, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11261eef85e22149</t>
+          <t>https://www.indeed.com/viewjob?jk=735a6235675ac15c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LoopNet</t>
+          <t>Senior DevOps/SRE Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3e215170f77dd53</t>
+          <t>https://www.indeed.com/viewjob?jk=188b1c3ac78beb01</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Cloud Data Solutions</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Coral Springs, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,172 +1616,172 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c874c000ec76150</t>
+          <t>https://www.indeed.com/viewjob?jk=669507442371cba5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c4f20a82a492aa</t>
+          <t>https://www.indeed.com/viewjob?jk=67a75da7f8d02636</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6aa2dd2deec446d</t>
+          <t>https://www.indeed.com/viewjob?jk=2a10b5deeed57fb5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Associate, Data Operations</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bank OZK</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e643dff32a837e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=74172d3e99aa20dd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OXIO</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Kafka, Cassandra, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df838957caceea8b</t>
+          <t>https://www.indeed.com/viewjob?jk=fc75e52ec0c2d0a5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008164574e63eb0f</t>
+          <t>https://www.indeed.com/viewjob?jk=e442b1efc55de33f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NICE Actimize Developer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,102 +1826,102 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7951d51dfc116951</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd2755f6f579f1e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Guidewire Developer (PolicyCenter)</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3929e9d9282e947</t>
+          <t>https://www.indeed.com/viewjob?jk=2f69e0df39814636</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Dir Data Warehouse Engineering</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brea, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653989f90deb93eb</t>
+          <t>https://www.indeed.com/viewjob?jk=17e79a4a8aebbe0c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Summer Associate Internship (Fraud Data Governance)</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa247b105a8195a</t>
+          <t>https://www.indeed.com/viewjob?jk=ac087a17c748782d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Summer Associate Internship (Business Intelligence Analyst)</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4613876632d673e6</t>
+          <t>https://www.indeed.com/viewjob?jk=4d781344d29a08f9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Analytics Platform Engineer</t>
+          <t>Senior Software Engineer - LoopNet</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e2fb702c156b62</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e215170f77dd53</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineering MTS</t>
+          <t>Senior Software Engineer – Cloud Data Solutions</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Coral Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,112 +2026,112 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bbe5469b433e310</t>
+          <t>https://www.indeed.com/viewjob?jk=4c874c000ec76150</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Summer Associate Internship (Associate Data Engineer)</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa822ad66fbbecb6</t>
+          <t>https://www.indeed.com/viewjob?jk=14c4f20a82a492aa</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0de49c5b0005920d</t>
+          <t>https://www.indeed.com/viewjob?jk=b6aa2dd2deec446d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Data Integration Engineer</t>
+          <t>Associate, Data Operations</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Compeer Financial</t>
+          <t>Bank OZK</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,137 +2141,137 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f769482011075d</t>
+          <t>https://www.indeed.com/viewjob?jk=e643dff32a837e1d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Guidewire Developer (PolicyCenter)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b7b991704ba53d</t>
+          <t>https://www.indeed.com/viewjob?jk=f3929e9d9282e947</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Solution Engineer - Remote</t>
+          <t>Dir Data Warehouse Engineering</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brea, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=549bd67dfaf059ff</t>
+          <t>https://www.indeed.com/viewjob?jk=653989f90deb93eb</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud Back End Engineer</t>
+          <t>Analytics Platform Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979c2d51bf327a22</t>
+          <t>https://www.indeed.com/viewjob?jk=17e2fb702c156b62</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mule ESB Developer</t>
+          <t>Software Engineering MTS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,67 +2281,67 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2602c0fe6a2e7651</t>
+          <t>https://www.indeed.com/viewjob?jk=2bbe5469b433e310</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Integration Platform Developer</t>
+          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d8e2b60f9187848</t>
+          <t>https://www.indeed.com/viewjob?jk=008164574e63eb0f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Summer Associate Internship (Fraud Data Governance)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=223035fc7a8a7be0</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa247b105a8195a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Summer Associate Internship (Business Intelligence Analyst)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Jenkins, Terraform, Docker</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f59d1ec1d618a17</t>
+          <t>https://www.indeed.com/viewjob?jk=4613876632d673e6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>Summer Associate Internship (Associate Data Engineer)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The Consortium Inc.</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, MySQL, dbt, CI/CD, Terraform, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,102 +2421,102 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04e6bb06610c32bf</t>
+          <t>https://www.indeed.com/viewjob?jk=fa822ad66fbbecb6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Windchill Technical Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60463e64c21c500</t>
+          <t>https://www.indeed.com/viewjob?jk=0de49c5b0005920d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capital Blue Cross</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ae2c6ad8ac24f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b7b991704ba53d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Base Administrator</t>
+          <t>Cloud Back End Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Big D Companies</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06360615fbf9de3a</t>
+          <t>https://www.indeed.com/viewjob?jk=979c2d51bf327a22</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ETL Tester with AI Experience</t>
+          <t>Integration Platform Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, dbt, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d0d3ecc1106859</t>
+          <t>https://www.indeed.com/viewjob?jk=8d8e2b60f9187848</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>OSS Engineer (US - Remote)</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Axon Networks</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, AKS, Git</t>
+          <t>Azure, Event Hubs, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=110b991660ad2978</t>
+          <t>https://www.indeed.com/viewjob?jk=eb93157183e3b612</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Quality Assurance Automation Engineer (C#)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Innocito Technologies Pvt Ltd</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Maven, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,89 +2631,89 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1858e1faf18bf984</t>
+          <t>https://www.indeed.com/viewjob?jk=223035fc7a8a7be0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Solution Engineer - Remote</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Lackland AFB, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Hive, Impala, Spark, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c235a4e1abd13f7</t>
+          <t>https://www.indeed.com/viewjob?jk=549bd67dfaf059ff</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Summer Associate Internship (Data Engineer)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, ETL, ELT, Python</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea20d1b92e7c4c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=2f59d1ec1d618a17</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Senior Security Engineer, Detection &amp; Response</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Aircall</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2722,11 +2722,11 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Athena, IAM, RDS, Azure, Databricks, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2390c91100957431</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae0266885ac8547</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Data Statistician</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, ETL, MLOps, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,102 +2771,102 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410d6c6a010f035c</t>
+          <t>https://www.indeed.com/viewjob?jk=a59b98e9d736a6c8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Cloud Network Engineer</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>KINECTIVE</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c91e3acfe1355358</t>
+          <t>https://www.indeed.com/viewjob?jk=24bdfee16835ece7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Azure Architect - Managed Services</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Lackland AFB, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Hive, Impala, Spark, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7090249009d0d6da</t>
+          <t>https://www.indeed.com/viewjob?jk=1d9680f06d024613</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Backend (Product &amp; Cloud Security)</t>
+          <t>Senior Solutions Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Yoodli AI Roleplays</t>
+          <t>Capital Blue Cross</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, NoSQL, Tableau, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,14 +2876,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9874984dfeed8f80</t>
+          <t>https://www.indeed.com/viewjob?jk=5ae2c6ad8ac24f2e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Windchill Technical Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2897,11 +2897,11 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf21b46341bfdf2</t>
+          <t>https://www.indeed.com/viewjob?jk=b60463e64c21c500</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Solutions Architect - Digital Native Business (Healthtech)</t>
+          <t>AI/ML Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Mars Technominds</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Git, Python</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,67 +2946,67 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11453f277a40e0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=9f5d7e731531139c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Microsoft Azure Specialist</t>
+          <t>ETL Tester with AI Exp</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, dbt, MLflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5427c3decfca9bb</t>
+          <t>https://www.indeed.com/viewjob?jk=4c20717958974031</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Engineer, Enterprise AI Platform</t>
+          <t>Data Base Administrator</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Camping World</t>
+          <t>Big D Companies</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, Azure, GCP, Snowflake, Data Modeling, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d593ed18a7eaef04</t>
+          <t>https://www.indeed.com/viewjob?jk=06360615fbf9de3a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AI Engineer, Enterprise AI Platform</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Camping World</t>
+          <t>VSCO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Lincolnshire, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, Azure, GCP, Snowflake, Data Modeling, MLflow, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Kafka, Snowflake, MySQL, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,59 +3051,59 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee18a654788e5998</t>
+          <t>https://www.indeed.com/viewjob?jk=c4c9e239c02c708b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>IT Analyst III - Senior Test Automation Engineer</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>State of Utah</t>
+          <t>The Consortium Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, MySQL, dbt, CI/CD, Terraform, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25024b299f02a2f9</t>
+          <t>https://www.indeed.com/viewjob?jk=04e6bb06610c32bf</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Systems Engineer - IT Data Management</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LEADER BANK</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Arlington, MA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, CI/CD, Git, CloudWatch</t>
+          <t>RDS, BigQuery, Dataflow, HBase, Kafka, Oracle, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21460f2f100edf5</t>
+          <t>https://www.indeed.com/viewjob?jk=61e0074bda774516</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Network Support &amp; Automation Engineer</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,15 +3146,400 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=410d6c6a010f035c</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Summer Associate Internship (Data Engineer)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Navy Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Vienna, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, ETL, ELT, Python</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea20d1b92e7c4c0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Sr Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Happen Bank</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2390c91100957431</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Cloud Network Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>KINECTIVE</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Golden, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c91e3acfe1355358</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a015b3f5ba31232</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Solutions Architect - Digital Native Business (Healthtech)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Git, Python</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11453f277a40e0ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer- Backend (Product &amp; Cloud Security)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Yoodli AI Roleplays</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, NoSQL, Tableau, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9874984dfeed8f80</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>IT Analyst III - Senior Test Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>State of Utah</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Jenkins</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=25024b299f02a2f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>AI Engineer, Enterprise AI Platform</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Camping World</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, ECS, Azure, GCP, Snowflake, Data Modeling, MLflow, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d593ed18a7eaef04</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>AI Engineer, Enterprise AI Platform</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Camping World</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Lincolnshire, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, ECS, Azure, GCP, Snowflake, Data Modeling, MLflow, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee18a654788e5998</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Evinova</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>AstraZeneca</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Gaithersburg, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, RDS, Kafka, PostgreSQL, MongoDB, DynamoDB, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0631723e82c79799</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Network Support &amp; Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=721f751b91f07d44</t>
         </is>
